--- a/design/templates/generated/North_Central/IRRIGATION_WATER_DROUGHT_NCE_V1_upload_template.xlsx
+++ b/design/templates/generated/North_Central/IRRIGATION_WATER_DROUGHT_NCE_V1_upload_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2020-2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2021-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-2030" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEIGHTS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_META" sheetId="5" state="hidden" r:id="rId5"/>
@@ -556,7 +556,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2020-2025 - Water Sector / Irrigation Water - Drought - North Central Province   [profile IRRIGATION_WATER_DROUGHT_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2021-2025 - Water Sector / Irrigation Water - Drought - North Central Province   [profile IRRIGATION_WATER_DROUGHT_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2025</v>
@@ -784,7 +784,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2020-2025</t>
+          <t>Dept. report 2021-2025</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>NCE-001</t>
+          <t>AN1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2025</v>
@@ -830,7 +830,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>NCE-002</t>
+          <t>AN2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2025</v>
@@ -864,7 +864,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NCE-003</t>
+          <t>AN3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2025</v>
@@ -898,7 +898,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>NCE-004</t>
+          <t>AN4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2025</v>
@@ -932,7 +932,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NCE-005</t>
+          <t>AN5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2025</v>
@@ -966,7 +966,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NCE-006</t>
+          <t>AN6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2025</v>
@@ -1000,7 +1000,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>NCE-007</t>
+          <t>AN7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2025</v>
@@ -1034,7 +1034,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NCE-008</t>
+          <t>AN8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2025</v>
@@ -1068,7 +1068,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>NCE-009</t>
+          <t>AN9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2025</v>
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NCE-010</t>
+          <t>AN10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2025</v>
@@ -1136,7 +1136,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NCE-011</t>
+          <t>AN11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2025</v>
@@ -1170,7 +1170,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NCE-012</t>
+          <t>AN12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2025</v>
@@ -1204,7 +1204,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NCE-013</t>
+          <t>AN13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2025</v>
@@ -1238,7 +1238,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NCE-014</t>
+          <t>AN14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2025</v>
@@ -1272,7 +1272,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>NCE-015</t>
+          <t>AN15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2025</v>
@@ -1306,7 +1306,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NCE-016</t>
+          <t>AN16</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2025</v>
@@ -1340,7 +1340,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NCE-017</t>
+          <t>AN17</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2025</v>
@@ -1374,7 +1374,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NCE-018</t>
+          <t>AN18</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2025</v>
@@ -1408,7 +1408,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NCE-019</t>
+          <t>AN19</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2025</v>
@@ -1442,7 +1442,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>NCE-020</t>
+          <t>AN20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2025</v>
@@ -1476,7 +1476,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NCE-021</t>
+          <t>AN21</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2025</v>
@@ -1510,7 +1510,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>NCE-022</t>
+          <t>AN22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2025</v>
@@ -1544,7 +1544,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NCE-023</t>
+          <t>PO1</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2025</v>
@@ -1578,7 +1578,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NCE-024</t>
+          <t>PO2</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2025</v>
@@ -1612,7 +1612,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>NCE-025</t>
+          <t>PO3</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2025</v>
@@ -1646,7 +1646,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NCE-026</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2025</v>
@@ -1680,7 +1680,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>NCE-027</t>
+          <t>PO5</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2025</v>
@@ -1714,7 +1714,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NCE-028</t>
+          <t>PO6</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2025</v>
@@ -1748,7 +1748,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>NCE-029</t>
+          <t>PO7</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2025</v>
@@ -1780,7 +1780,6 @@
       <c r="P33" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -1823,7 +1822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2025-2030 - Water Sector / Irrigation Water - Drought - North Central Province   [profile IRRIGATION_WATER_DROUGHT_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2026-2030 - Water Sector / Irrigation Water - Drought - North Central Province   [profile IRRIGATION_WATER_DROUGHT_NCE_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2016,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2030</v>
@@ -2051,7 +2050,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2025-2030</t>
+          <t>Dept. report 2026-2030</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
@@ -2063,7 +2062,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>NCE-001</t>
+          <t>AN1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -2077,7 +2076,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2030</v>
@@ -2097,7 +2096,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>NCE-002</t>
+          <t>AN2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2111,7 +2110,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2030</v>
@@ -2131,7 +2130,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NCE-003</t>
+          <t>AN3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -2145,7 +2144,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2030</v>
@@ -2165,7 +2164,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>NCE-004</t>
+          <t>AN4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2179,7 +2178,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2030</v>
@@ -2199,7 +2198,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NCE-005</t>
+          <t>AN5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -2213,7 +2212,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2030</v>
@@ -2233,7 +2232,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NCE-006</t>
+          <t>AN6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -2247,7 +2246,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2030</v>
@@ -2267,7 +2266,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>NCE-007</t>
+          <t>AN7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -2281,7 +2280,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2030</v>
@@ -2301,7 +2300,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NCE-008</t>
+          <t>AN8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -2315,7 +2314,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2030</v>
@@ -2335,7 +2334,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>NCE-009</t>
+          <t>AN9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -2349,7 +2348,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2030</v>
@@ -2369,7 +2368,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NCE-010</t>
+          <t>AN10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -2383,7 +2382,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2030</v>
@@ -2403,7 +2402,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NCE-011</t>
+          <t>AN11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -2417,7 +2416,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2030</v>
@@ -2437,7 +2436,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NCE-012</t>
+          <t>AN12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -2451,7 +2450,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2030</v>
@@ -2471,7 +2470,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NCE-013</t>
+          <t>AN13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -2485,7 +2484,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2030</v>
@@ -2505,7 +2504,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NCE-014</t>
+          <t>AN14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -2519,7 +2518,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2030</v>
@@ -2539,7 +2538,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>NCE-015</t>
+          <t>AN15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -2553,7 +2552,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2030</v>
@@ -2573,7 +2572,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NCE-016</t>
+          <t>AN16</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -2587,7 +2586,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2030</v>
@@ -2607,7 +2606,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NCE-017</t>
+          <t>AN17</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -2621,7 +2620,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2030</v>
@@ -2641,7 +2640,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NCE-018</t>
+          <t>AN18</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -2655,7 +2654,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2030</v>
@@ -2675,7 +2674,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NCE-019</t>
+          <t>AN19</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -2689,7 +2688,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2030</v>
@@ -2709,7 +2708,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>NCE-020</t>
+          <t>AN20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -2723,7 +2722,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2030</v>
@@ -2743,7 +2742,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NCE-021</t>
+          <t>AN21</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2757,7 +2756,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2030</v>
@@ -2777,7 +2776,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>NCE-022</t>
+          <t>AN22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -2791,7 +2790,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2030</v>
@@ -2811,7 +2810,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NCE-023</t>
+          <t>PO1</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2825,7 +2824,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2030</v>
@@ -2845,7 +2844,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NCE-024</t>
+          <t>PO2</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2859,7 +2858,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2030</v>
@@ -2879,7 +2878,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>NCE-025</t>
+          <t>PO3</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2893,7 +2892,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2030</v>
@@ -2913,7 +2912,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NCE-026</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -2927,7 +2926,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2030</v>
@@ -2947,7 +2946,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>NCE-027</t>
+          <t>PO5</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2961,7 +2960,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2030</v>
@@ -2981,7 +2980,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NCE-028</t>
+          <t>PO6</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2995,7 +2994,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2030</v>
@@ -3015,7 +3014,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>NCE-029</t>
+          <t>PO7</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -3029,7 +3028,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2030</v>
@@ -3047,7 +3046,6 @@
       <c r="P33" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3066,7 +3064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3075,6 +3073,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3122,6 +3121,11 @@
           <t>PROPOSED WEIGHT % (read at import)</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>basis of the proposal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -3142,6 +3146,7 @@
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="12" t="n"/>
+      <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -3170,6 +3175,7 @@
       <c r="F5" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="G5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -3190,6 +3196,7 @@
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="12" t="n"/>
+      <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -3210,6 +3217,7 @@
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
+      <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -3230,6 +3238,7 @@
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
+      <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -3258,6 +3267,7 @@
       <c r="F9" s="12" t="n">
         <v>30</v>
       </c>
+      <c r="G9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -3286,6 +3296,7 @@
       <c r="F10" s="12" t="n">
         <v>40</v>
       </c>
+      <c r="G10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -3314,6 +3325,7 @@
       <c r="F11" s="12" t="n">
         <v>30</v>
       </c>
+      <c r="G11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -3334,6 +3346,7 @@
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="12" t="n"/>
+      <c r="G12" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -3358,9 +3371,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
@@ -3399,14 +3411,14 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: IRRIGATION_WATER_DROUGHT_NCE_V1   |   generated 2026-07-29 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: IRRIGATION_WATER_DROUGHT_NCE_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>1. One tab per data period (2020-2025, 2025-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
+          <t>1. One tab per data period (2021-2025, 2026-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
         </is>
       </c>
     </row>
@@ -3420,14 +3432,14 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2b. The year 2025 appears in both tabs. If a year sits in two periods the system uses the LATER period's value, so nothing is counted twice.</t>
+          <t>2b. The two periods are contiguous and do not overlap (changed 2026-09-03 at the Central panel's request - the old 2020-2025 / 2025-2030 pair shared the year 2025 and needed a tie-break). Every year belongs to exactly one tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>3. Edit ONLY the yellow cells. Division codes, names, district and the period columns are pre-filled and locked.</t>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3453,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Do not add, remove, rename or reorder columns or tabs. Files with changed structure are rejected on import.</t>
+          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3851,80 +3863,104 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>generated</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>unlocked-review</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dsd_level</t>
+          <t>panel_overrides</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>DS_DIVISION</t>
+          <t>0 add, 0 retire</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>periods</t>
+          <t>generated</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2020-2025|2025-2030</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>n_variables</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>9</v>
+          <t>dsd_level</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>DS_DIVISION</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>period_rule_default</t>
+          <t>periods</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>average (typical year); 2025 -&gt; latest period wins</t>
+          <t>2021-2025|2026-2030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>period_aggregation</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>DROUGHT_EVENTS_1974_TO_2022=fixed_window|DROUGHT_HAZARD_INDEX=fixed_window|OCCURRENCE_WARM_DAYS=fixed_window|STANDARD_PRECIPITATION_INDEX=fixed_window|EXISTING_MINOR_IRRI_SCHEMES=average|FARM_HOUSEHOLDS_POPULATION=average|IRRIGATED_PADDY_AREA=average|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022=max|PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT=average</t>
-        </is>
+          <t>n_variables</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
+          <t>period_rule_default</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>average (typical year); periods are contiguous, no overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>period_aggregation</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>DROUGHT_EVENTS_1974_TO_2022=fixed_window|DROUGHT_HAZARD_INDEX=fixed_window|OCCURRENCE_WARM_DAYS=fixed_window|STANDARD_PRECIPITATION_INDEX=fixed_window|EXISTING_MINOR_IRRI_SCHEMES=average|FARM_HOUSEHOLDS_POPULATION=average|IRRIGATED_PADDY_AREA=average|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022=max|PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT=average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>expected_columns</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|DROUGHT_EVENTS_1974_TO_2022|DROUGHT_HAZARD_INDEX|OCCURRENCE_WARM_DAYS|STANDARD_PRECIPITATION_INDEX|EXISTING_MINOR_IRRI_SCHEMES|FARM_HOUSEHOLDS_POPULATION|IRRIGATED_PADDY_AREA|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022|PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT|DATA_SOURCE|NOTES</t>
         </is>

--- a/design/templates/generated/North_Central/IRRIGATION_WATER_DROUGHT_NCE_V1_upload_template.xlsx
+++ b/design/templates/generated/North_Central/IRRIGATION_WATER_DROUGHT_NCE_V1_upload_template.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -551,6 +551,9 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,55 +591,70 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>DROUGHT_EVENTS_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>DROUGHT_EVENTS_1974_TO_2022</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>DROUGHT_EVENTS_2005_TO_2022</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>DROUGHT_HAZARD_INDEX</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>OCCURRENCE_WARM_DAYS</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>STANDARD_PRECIPITATION_INDEX</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>EXISTING_MINOR_IRRI_SCHEMES</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>FARM_HOUSEHOLDS_POPULATION</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>IRRIGATED_PADDY_AREA</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_2005_TO_2022</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>DATA_SOURCE</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -670,64 +688,82 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>hazard: No. of Drought events - 1974 to 2004 (25%)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>hazard: No. of drought events - 1974 to 2022 (1974-2004, 25%, 2005 -2022, 75%)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: No. of Drought events - 2005 -2022 (75%)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>hazard: Drought Hazard  Index
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>hazard: Occurrence of warm days (TX90p)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>hazard: SPI (Intensity)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Existing Minor Irri. Schemes
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>exposure: Farm household's population
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>exposure: Total irrigated paddy area
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>exposure: Max # of Drought affected People during 1974 to 2022 (1974 -2004, 25%, 2005 -2022, 75%)
-&gt;&gt; enter the MAXIMUM (already a fixed-window figure)</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>exposure: Max # of drought affected People - 1974 to 2004 (25%)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>exposure: Max # of drought affected People - 2005 to 2022 (75%)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>exposure: % of total irrigated paddy area from total paddy extent
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>origin of the numbers</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
@@ -782,12 +818,21 @@
       <c r="N4" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Dept. report 2021-2025</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>example row</t>
         </is>
@@ -826,6 +871,9 @@
       <c r="N5" s="8" t="n"/>
       <c r="O5" s="8" t="n"/>
       <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="n"/>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -860,6 +908,9 @@
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
       <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -894,6 +945,9 @@
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="8" t="n"/>
       <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -928,6 +982,9 @@
       <c r="N8" s="8" t="n"/>
       <c r="O8" s="8" t="n"/>
       <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -962,6 +1019,9 @@
       <c r="N9" s="8" t="n"/>
       <c r="O9" s="8" t="n"/>
       <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="n"/>
+      <c r="R9" s="8" t="n"/>
+      <c r="S9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -996,6 +1056,9 @@
       <c r="N10" s="8" t="n"/>
       <c r="O10" s="8" t="n"/>
       <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1030,6 +1093,9 @@
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n"/>
       <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1064,6 +1130,9 @@
       <c r="N12" s="8" t="n"/>
       <c r="O12" s="8" t="n"/>
       <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1098,6 +1167,9 @@
       <c r="N13" s="8" t="n"/>
       <c r="O13" s="8" t="n"/>
       <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1132,6 +1204,9 @@
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
       <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1166,6 +1241,9 @@
       <c r="N15" s="8" t="n"/>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="n"/>
+      <c r="R15" s="8" t="n"/>
+      <c r="S15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1200,6 +1278,9 @@
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n"/>
       <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1234,6 +1315,9 @@
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="n"/>
       <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1268,6 +1352,9 @@
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="8" t="n"/>
+      <c r="S18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1302,6 +1389,9 @@
       <c r="N19" s="8" t="n"/>
       <c r="O19" s="8" t="n"/>
       <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1336,6 +1426,9 @@
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1370,6 +1463,9 @@
       <c r="N21" s="8" t="n"/>
       <c r="O21" s="8" t="n"/>
       <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="8" t="n"/>
+      <c r="R21" s="8" t="n"/>
+      <c r="S21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1404,6 +1500,9 @@
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="8" t="n"/>
+      <c r="S22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1438,6 +1537,9 @@
       <c r="N23" s="8" t="n"/>
       <c r="O23" s="8" t="n"/>
       <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="8" t="n"/>
+      <c r="S23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1472,6 +1574,9 @@
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="8" t="n"/>
+      <c r="S24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1506,6 +1611,9 @@
       <c r="N25" s="8" t="n"/>
       <c r="O25" s="8" t="n"/>
       <c r="P25" s="8" t="n"/>
+      <c r="Q25" s="8" t="n"/>
+      <c r="R25" s="8" t="n"/>
+      <c r="S25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1540,6 +1648,9 @@
       <c r="N26" s="8" t="n"/>
       <c r="O26" s="8" t="n"/>
       <c r="P26" s="8" t="n"/>
+      <c r="Q26" s="8" t="n"/>
+      <c r="R26" s="8" t="n"/>
+      <c r="S26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -1574,6 +1685,9 @@
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="8" t="n"/>
+      <c r="R27" s="8" t="n"/>
+      <c r="S27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -1608,6 +1722,9 @@
       <c r="N28" s="8" t="n"/>
       <c r="O28" s="8" t="n"/>
       <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="8" t="n"/>
+      <c r="R28" s="8" t="n"/>
+      <c r="S28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -1642,6 +1759,9 @@
       <c r="N29" s="8" t="n"/>
       <c r="O29" s="8" t="n"/>
       <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="8" t="n"/>
+      <c r="R29" s="8" t="n"/>
+      <c r="S29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -1676,6 +1796,9 @@
       <c r="N30" s="8" t="n"/>
       <c r="O30" s="8" t="n"/>
       <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="8" t="n"/>
+      <c r="R30" s="8" t="n"/>
+      <c r="S30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1710,6 +1833,9 @@
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="n"/>
       <c r="P31" s="8" t="n"/>
+      <c r="Q31" s="8" t="n"/>
+      <c r="R31" s="8" t="n"/>
+      <c r="S31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -1744,6 +1870,9 @@
       <c r="N32" s="8" t="n"/>
       <c r="O32" s="8" t="n"/>
       <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="8" t="n"/>
+      <c r="R32" s="8" t="n"/>
+      <c r="S32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -1778,13 +1907,16 @@
       <c r="N33" s="8" t="n"/>
       <c r="O33" s="8" t="n"/>
       <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="8" t="n"/>
+      <c r="R33" s="8" t="n"/>
+      <c r="S33" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1798,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1817,6 +1949,9 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1854,55 +1989,70 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>DROUGHT_EVENTS_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>DROUGHT_EVENTS_1974_TO_2022</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>DROUGHT_EVENTS_2005_TO_2022</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>DROUGHT_HAZARD_INDEX</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>OCCURRENCE_WARM_DAYS</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>STANDARD_PRECIPITATION_INDEX</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>EXISTING_MINOR_IRRI_SCHEMES</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>FARM_HOUSEHOLDS_POPULATION</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>IRRIGATED_PADDY_AREA</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_2005_TO_2022</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>DATA_SOURCE</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -1936,64 +2086,82 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>hazard: No. of Drought events - 1974 to 2004 (25%)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>hazard: No. of drought events - 1974 to 2022 (1974-2004, 25%, 2005 -2022, 75%)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: No. of Drought events - 2005 -2022 (75%)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>hazard: Drought Hazard  Index
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>hazard: Occurrence of warm days (TX90p)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>hazard: SPI (Intensity)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>exposure: No. of Existing Minor Irri. Schemes
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>exposure: Farm household's population
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>exposure: Total irrigated paddy area
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>exposure: Max # of Drought affected People during 1974 to 2022 (1974 -2004, 25%, 2005 -2022, 75%)
-&gt;&gt; enter the MAXIMUM (already a fixed-window figure)</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>exposure: Max # of drought affected People - 1974 to 2004 (25%)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>exposure: Max # of drought affected People - 2005 to 2022 (75%)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>exposure: % of total irrigated paddy area from total paddy extent
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>origin of the numbers</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
@@ -2048,12 +2216,21 @@
       <c r="N4" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Dept. report 2026-2030</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>example row</t>
         </is>
@@ -2092,6 +2269,9 @@
       <c r="N5" s="8" t="n"/>
       <c r="O5" s="8" t="n"/>
       <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="n"/>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2126,6 +2306,9 @@
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
       <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2160,6 +2343,9 @@
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="8" t="n"/>
       <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2194,6 +2380,9 @@
       <c r="N8" s="8" t="n"/>
       <c r="O8" s="8" t="n"/>
       <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2228,6 +2417,9 @@
       <c r="N9" s="8" t="n"/>
       <c r="O9" s="8" t="n"/>
       <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="n"/>
+      <c r="R9" s="8" t="n"/>
+      <c r="S9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2262,6 +2454,9 @@
       <c r="N10" s="8" t="n"/>
       <c r="O10" s="8" t="n"/>
       <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2296,6 +2491,9 @@
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n"/>
       <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2330,6 +2528,9 @@
       <c r="N12" s="8" t="n"/>
       <c r="O12" s="8" t="n"/>
       <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2364,6 +2565,9 @@
       <c r="N13" s="8" t="n"/>
       <c r="O13" s="8" t="n"/>
       <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2398,6 +2602,9 @@
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
       <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2432,6 +2639,9 @@
       <c r="N15" s="8" t="n"/>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="n"/>
+      <c r="R15" s="8" t="n"/>
+      <c r="S15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -2466,6 +2676,9 @@
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n"/>
       <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -2500,6 +2713,9 @@
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="n"/>
       <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -2534,6 +2750,9 @@
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="8" t="n"/>
+      <c r="S18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2568,6 +2787,9 @@
       <c r="N19" s="8" t="n"/>
       <c r="O19" s="8" t="n"/>
       <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -2602,6 +2824,9 @@
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -2636,6 +2861,9 @@
       <c r="N21" s="8" t="n"/>
       <c r="O21" s="8" t="n"/>
       <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="8" t="n"/>
+      <c r="R21" s="8" t="n"/>
+      <c r="S21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -2670,6 +2898,9 @@
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="8" t="n"/>
+      <c r="S22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -2704,6 +2935,9 @@
       <c r="N23" s="8" t="n"/>
       <c r="O23" s="8" t="n"/>
       <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="8" t="n"/>
+      <c r="S23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -2738,6 +2972,9 @@
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="8" t="n"/>
+      <c r="S24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2772,6 +3009,9 @@
       <c r="N25" s="8" t="n"/>
       <c r="O25" s="8" t="n"/>
       <c r="P25" s="8" t="n"/>
+      <c r="Q25" s="8" t="n"/>
+      <c r="R25" s="8" t="n"/>
+      <c r="S25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -2806,6 +3046,9 @@
       <c r="N26" s="8" t="n"/>
       <c r="O26" s="8" t="n"/>
       <c r="P26" s="8" t="n"/>
+      <c r="Q26" s="8" t="n"/>
+      <c r="R26" s="8" t="n"/>
+      <c r="S26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -2840,6 +3083,9 @@
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="8" t="n"/>
+      <c r="R27" s="8" t="n"/>
+      <c r="S27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -2874,6 +3120,9 @@
       <c r="N28" s="8" t="n"/>
       <c r="O28" s="8" t="n"/>
       <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="8" t="n"/>
+      <c r="R28" s="8" t="n"/>
+      <c r="S28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -2908,6 +3157,9 @@
       <c r="N29" s="8" t="n"/>
       <c r="O29" s="8" t="n"/>
       <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="8" t="n"/>
+      <c r="R29" s="8" t="n"/>
+      <c r="S29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -2942,6 +3194,9 @@
       <c r="N30" s="8" t="n"/>
       <c r="O30" s="8" t="n"/>
       <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="8" t="n"/>
+      <c r="R30" s="8" t="n"/>
+      <c r="S30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -2976,6 +3231,9 @@
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="n"/>
       <c r="P31" s="8" t="n"/>
+      <c r="Q31" s="8" t="n"/>
+      <c r="R31" s="8" t="n"/>
+      <c r="S31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -3010,6 +3268,9 @@
       <c r="N32" s="8" t="n"/>
       <c r="O32" s="8" t="n"/>
       <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="8" t="n"/>
+      <c r="R32" s="8" t="n"/>
+      <c r="S32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -3044,13 +3305,16 @@
       <c r="N33" s="8" t="n"/>
       <c r="O33" s="8" t="n"/>
       <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="8" t="n"/>
+      <c r="R33" s="8" t="n"/>
+      <c r="S33" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -3064,7 +3328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3130,12 +3394,12 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>DROUGHT_EVENTS_1974_TO_2022</t>
+          <t>DROUGHT_EVENTS_1974_TO_2004</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>No. of drought events - 1974 to 2022 (1974-2004, 25%, 2005 -2022, 75%)</t>
+          <t>No. of Drought events - 1974 to 2004 (25%)</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -3149,43 +3413,35 @@
       <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>DROUGHT_HAZARD_INDEX</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Drought Hazard  Index</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>DROUGHT_EVENTS_1974_TO_2022</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>No. of drought events - 1974 to 2022 (1974-2004, 25%, 2005 -2022, 75%)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>hazard</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="13" t="inlineStr"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>OCCURRENCE_WARM_DAYS</t>
+          <t>DROUGHT_EVENTS_2005_TO_2022</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Occurrence of warm days (TX90p)</t>
+          <t>No. of Drought events - 2005 -2022 (75%)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -3199,40 +3455,48 @@
       <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>STANDARD_PRECIPITATION_INDEX</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>SPI (Intensity)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>DROUGHT_HAZARD_INDEX</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Drought Hazard  Index</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>hazard</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="11" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>EXISTING_MINOR_IRRI_SCHEMES</t>
+          <t>OCCURRENCE_WARM_DAYS</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>No. of Existing Minor Irri. Schemes</t>
+          <t>Occurrence of warm days (TX90p)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -3241,72 +3505,56 @@
       <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>FARM_HOUSEHOLDS_POPULATION</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Farm household's population</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>STANDARD_PRECIPITATION_INDEX</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>SPI (Intensity)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>EXISTING_MINOR_IRRI_SCHEMES</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>No. of Existing Minor Irri. Schemes</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>IRRIGATED_PADDY_AREA</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Total irrigated paddy area</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022</t>
+          <t>FARM_HOUSEHOLDS_POPULATION</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Max # of Drought affected People during 1974 to 2022 (1974 -2004, 25%, 2005 -2022, 75%)</t>
+          <t>Farm household's population</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -3328,45 +3576,128 @@
       <c r="G11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>IRRIGATED_PADDY_AREA</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Total irrigated paddy area</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Max # of drought affected People - 1974 to 2004 (25%)</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>derived: 25% of retired MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022 (30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_2005_TO_2022</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Max # of drought affected People - 2005 to 2022 (75%)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>derived: 75% of retired MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022 (30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>% of total irrigated paddy area from total paddy extent</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="11" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="11" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>SUM - hazard (must equal 100)</t>
         </is>
       </c>
-      <c r="F14" s="15">
-        <f>F4+F5+F6+F7</f>
+      <c r="F17" s="15">
+        <f>F4+F5+F6+F7+F8+F9</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>SUM - exposure (must equal 100)</t>
         </is>
       </c>
-      <c r="F15" s="15">
-        <f>F8+F9+F10+F11+F12</f>
+      <c r="F18" s="15">
+        <f>F10+F11+F12+F13+F14+F15</f>
         <v/>
       </c>
     </row>
@@ -3375,7 +3706,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -3390,7 +3721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3411,7 +3742,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: IRRIGATION_WATER_DROUGHT_NCE_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: IRRIGATION_WATER_DROUGHT_NCE_V1   |   generated 2026-09-14 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
@@ -3437,9 +3768,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>3. The yellow cells are where data belongs. Division codes, names, district and the period columns are pre-filled - change one only to correct a genuine error. Nothing in this file is protected, so please treat that as the instruction it is; the importer checks those columns and will refuse what it cannot match.</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3784,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
+          <t>5. Do not add, remove, rename or reorder columns or tabs. Excel will now let you - the sheet is not protected - but the importer will not: the hidden _META tab states this file's column contract and a file whose structure has changed is refused, naming what changed. Nothing loads partially, so a rejected file loads nothing at all.</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3858,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>DROUGHT_EVENTS_1974_TO_2022</t>
+          <t>DROUGHT_EVENTS_1974_TO_2004</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>No. of drought events - 1974 to 2022 (1974-2004, 25%, 2005 -2022, 75%)</t>
+          <t>No. of Drought events - 1974 to 2004 (25%)</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -3544,19 +3875,19 @@
       <c r="E18" s="13" t="n"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>fixed window - same value on both period tabs</t>
+          <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>DROUGHT_HAZARD_INDEX</t>
+          <t>DROUGHT_EVENTS_1974_TO_2022</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Drought Hazard  Index</t>
+          <t>No. of drought events - 1974 to 2022 (1974-2004, 25%, 2005 -2022, 75%)</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -3564,14 +3895,8 @@
           <t>hazard</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>100</v>
-      </c>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
           <t>fixed window - same value on both period tabs</t>
@@ -3581,12 +3906,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>OCCURRENCE_WARM_DAYS</t>
+          <t>DROUGHT_EVENTS_2005_TO_2022</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Occurrence of warm days (TX90p)</t>
+          <t>No. of Drought events - 2005 -2022 (75%)</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -3598,19 +3923,19 @@
       <c r="E20" s="13" t="n"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>fixed window - same value on both period tabs</t>
+          <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>STANDARD_PRECIPITATION_INDEX</t>
+          <t>DROUGHT_HAZARD_INDEX</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>SPI (Intensity)</t>
+          <t>Drought Hazard  Index</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -3618,8 +3943,14 @@
           <t>hazard</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
           <t>fixed window - same value on both period tabs</t>
@@ -3629,66 +3960,60 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>EXISTING_MINOR_IRRI_SCHEMES</t>
+          <t>OCCURRENCE_WARM_DAYS</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>No. of Existing Minor Irri. Schemes</t>
+          <t>Occurrence of warm days (TX90p)</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>enter a TYPICAL YEAR (not a total)</t>
+          <t>fixed window - same value on both period tabs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>FARM_HOUSEHOLDS_POPULATION</t>
+          <t>STANDARD_PRECIPITATION_INDEX</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Farm household's population</t>
+          <t>SPI (Intensity)</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>30</v>
-      </c>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>enter a TYPICAL YEAR (not a total)</t>
+          <t>fixed window - same value on both period tabs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>IRRIGATED_PADDY_AREA</t>
+          <t>EXISTING_MINOR_IRRI_SCHEMES</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Total irrigated paddy area</t>
+          <t>No. of Existing Minor Irri. Schemes</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -3696,14 +4021,8 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>40</v>
-      </c>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
       <c r="F24" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -3713,12 +4032,12 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022</t>
+          <t>FARM_HOUSEHOLDS_POPULATION</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Max # of Drought affected People during 1974 to 2022 (1974 -2004, 25%, 2005 -2022, 75%)</t>
+          <t>Farm household's population</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -3736,29 +4055,107 @@
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>enter the MAXIMUM (already a fixed-window figure)</t>
+          <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
+          <t>IRRIGATED_PADDY_AREA</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Total irrigated paddy area</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Max # of drought affected People - 1974 to 2004 (25%)</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_2005_TO_2022</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Max # of drought affected People - 2005 to 2022 (75%)</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
           <t>PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>% of total irrigated paddy area from total paddy extent</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
@@ -3868,7 +4265,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>unlocked-review</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -3880,7 +4277,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>0 add, 0 retire</t>
+          <t>4 add, 1 retire</t>
         </is>
       </c>
     </row>
@@ -3892,7 +4289,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -3927,7 +4324,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3950,7 +4347,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>DROUGHT_EVENTS_1974_TO_2022=fixed_window|DROUGHT_HAZARD_INDEX=fixed_window|OCCURRENCE_WARM_DAYS=fixed_window|STANDARD_PRECIPITATION_INDEX=fixed_window|EXISTING_MINOR_IRRI_SCHEMES=average|FARM_HOUSEHOLDS_POPULATION=average|IRRIGATED_PADDY_AREA=average|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022=max|PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT=average</t>
+          <t>DROUGHT_EVENTS_1974_TO_2004=average|DROUGHT_EVENTS_1974_TO_2022=fixed_window|DROUGHT_EVENTS_2005_TO_2022=average|DROUGHT_HAZARD_INDEX=fixed_window|OCCURRENCE_WARM_DAYS=fixed_window|STANDARD_PRECIPITATION_INDEX=fixed_window|EXISTING_MINOR_IRRI_SCHEMES=average|FARM_HOUSEHOLDS_POPULATION=average|IRRIGATED_PADDY_AREA=average|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2004=average|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_2005_TO_2022=average|PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT=average</t>
         </is>
       </c>
     </row>
@@ -3962,7 +4359,7 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|DROUGHT_EVENTS_1974_TO_2022|DROUGHT_HAZARD_INDEX|OCCURRENCE_WARM_DAYS|STANDARD_PRECIPITATION_INDEX|EXISTING_MINOR_IRRI_SCHEMES|FARM_HOUSEHOLDS_POPULATION|IRRIGATED_PADDY_AREA|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2022|PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT|DATA_SOURCE|NOTES</t>
+          <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|DROUGHT_EVENTS_1974_TO_2004|DROUGHT_EVENTS_1974_TO_2022|DROUGHT_EVENTS_2005_TO_2022|DROUGHT_HAZARD_INDEX|OCCURRENCE_WARM_DAYS|STANDARD_PRECIPITATION_INDEX|EXISTING_MINOR_IRRI_SCHEMES|FARM_HOUSEHOLDS_POPULATION|IRRIGATED_PADDY_AREA|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_1974_TO_2004|MAXIMUM_DROUGHT_AFFECTED_PEOPLE_DURING_2005_TO_2022|PCT_IRRIGATED_PADDY_AREA_PADDY_EXTENT|DATA_SOURCE|NOTES</t>
         </is>
       </c>
     </row>
